--- a/Archivos_Compartidos/Cursos RH/Ultimos Cursos/Curso Dos/Protección de Datos/Respuestas/Datos Personales respuestas.xlsx
+++ b/Archivos_Compartidos/Cursos RH/Ultimos Cursos/Curso Dos/Protección de Datos/Respuestas/Datos Personales respuestas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\N877991\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santandernet-my.sharepoint.com/personal/n854611_corp_santanderam_com/Documents/Documentos/GitHub/SAM_Santander/SAM_Santander/Archivos_Compartidos/Cursos RH/Ultimos Cursos/Curso Dos/Protección de Datos/Respuestas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BC10477-D361-442B-83DC-6B4B68531555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{0BC10477-D361-442B-83DC-6B4B68531555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F829139-99C4-4837-AFFE-94A98E3952BB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{4ED61198-4BA0-43C7-B840-EA5B44C2E322}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12810" windowHeight="15135" xr2:uid="{4ED61198-4BA0-43C7-B840-EA5B44C2E322}"/>
   </bookViews>
   <sheets>
     <sheet name="LFPDPPP" sheetId="2" r:id="rId1"/>
@@ -81,9 +81,6 @@
     <t>c. Cualquier derecho que te da la LFDPPP</t>
   </si>
   <si>
-    <t>4. Cual es el canal para ayudar a clientes, proveedores, empleados, exempleados, etc. Para que puedan proporcionar información para ejercer sus derechos ARCO?</t>
-  </si>
-  <si>
     <t>a. manual.conducta@santanderam.com</t>
   </si>
   <si>
@@ -93,23 +90,26 @@
     <t>b. pldycft@santanderam.com</t>
   </si>
   <si>
-    <t>5. Cuando puede negarse el ejecicio de los derechos ARCO?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a. Cuando exista un impedimento legal o resolución de una autoridad competente que limite su acceso o no permita la rectificación, cancelación u oposición </t>
-  </si>
-  <si>
     <t>b. Cuando un exempleado los solicita.</t>
   </si>
   <si>
     <t>c. Cuando un proveedor  los solicita.</t>
+  </si>
+  <si>
+    <t>4. ¿Cual es el canal para ayudar a clientes, proveedores, empleados, exempleados, etc. Para que puedan proporcionar información para ejercer sus derechos ARCO?</t>
+  </si>
+  <si>
+    <t>5. ¿Cuando puede negarse el ejecicio de los derechos ARCO?</t>
+  </si>
+  <si>
+    <t>a. Cuando exista un impedimento legal o resolución de una autoridad competente que limite su acceso o no permita la rectificación, cancelación u oposición.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,9 +196,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -236,7 +236,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -342,7 +342,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,7 +484,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -493,135 +493,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358B5D24-7ED2-476D-A092-1D2E4F6B2A20}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="82.85546875" customWidth="1"/>
     <col min="2" max="2" width="3.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="29.1">
+    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="1"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="29.1">
-      <c r="A25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="B27" s="1"/>
     </row>
@@ -634,7 +634,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB80AE-A8D6-410D-82A8-23EF268F0D3E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -785,12 +785,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -799,14 +793,43 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{872B7DB5-04DC-4D3C-9678-B1E315BF3A94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{872B7DB5-04DC-4D3C-9678-B1E315BF3A94}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6a3a5e9b-ee09-41e2-808a-978ed94a5e6b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F43C7E1-5490-4EDB-B49E-EB1D781AAB19}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EC03667-1D50-4E40-AF9C-3BF617DAF11A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EC03667-1D50-4E40-AF9C-3BF617DAF11A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F43C7E1-5490-4EDB-B49E-EB1D781AAB19}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>